--- a/mlef_pipeline/results/OS_24/C2/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_24/C2/training_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,803 +548,292 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD</t>
+          <t>RWD_DP_FMRAD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.699741753631335</v>
+        <v>0.8777674418604653</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04294965230512315</v>
+        <v>0.05848580668017112</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5802035706733421</v>
+        <v>0.7051114858677369</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04322119223765066</v>
+        <v>0.1019133186649609</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6357024506497079</v>
+        <v>0.7240981240981241</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07190410776816766</v>
+        <v>0.1378384406085342</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6278078577742572</v>
+        <v>0.7778709893048127</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04492451925603947</v>
+        <v>0.06697464551122141</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7625248015873015</v>
+        <v>0.7157894736842105</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08441832814998784</v>
+        <v>0.2147913896888859</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4460204463951186</v>
+        <v>0.5872235872235873</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9761904761904762</v>
+        <v>0.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6674645390070921</v>
+        <v>0.5421455938697318</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08795610769846374</v>
+        <v>0.1770295142267198</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4675531914893617</v>
+        <v>0.5220338983050847</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2234042553191489</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="T2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U2" t="n">
-        <v>800</v>
+        <v>168</v>
       </c>
       <c r="V2" t="n">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="W2" t="n">
-        <v>154</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_DP</t>
+          <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7658368666302843</v>
+        <v>0.6327441860465115</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05849608522914673</v>
+        <v>0.09877189114060714</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6340783025257245</v>
+        <v>0.3753086021903226</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07270509992870496</v>
+        <v>0.1508130617942004</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6941367151123248</v>
+        <v>0.6405328798185941</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05957787040229276</v>
+        <v>0.3790300093674511</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6968035361929945</v>
+        <v>0.4585795255602241</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1152292525216845</v>
+        <v>0.32794653767877</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7052631578947368</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1709979090437199</v>
+        <v>0.2581878322029749</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4033251231527094</v>
+        <v>0.5343915343915344</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6436657681940701</v>
+        <v>0.6877394636015325</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1201656784963364</v>
+        <v>0.1674592721583602</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4104062722736992</v>
+        <v>0.6168478260869565</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.5172413793103449</v>
       </c>
       <c r="T3" t="n">
         <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>370</v>
+        <v>168</v>
       </c>
       <c r="V3" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="W3" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP/rwd-only</t>
+          <t>RWD_DP_PYRAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.685949372402502</v>
+        <v>0.8010416666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06364853492737121</v>
+        <v>0.0816571350436609</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3949022674670311</v>
+        <v>0.6185683950304259</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1417848375409452</v>
+        <v>0.09959387504812622</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4191677391677391</v>
+        <v>0.627986875120633</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4269661044479011</v>
+        <v>0.05712198257942337</v>
       </c>
       <c r="H4" t="n">
-        <v>0.643038474832912</v>
+        <v>0.7046724740851755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3740835525841771</v>
+        <v>0.09348734701817422</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7101851851851853</v>
+        <v>0.7263157894736842</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1671256894253103</v>
+        <v>0.2497615775250961</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3081232492997199</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6177897574123989</v>
+        <v>0.7586206896551725</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1258110641412173</v>
+        <v>0.1414099721975188</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3854580309461865</v>
+        <v>0.6497764530551415</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1509433962264151</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="V4" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="W4" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD_DP_PYRAD/rwd-only</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7356837606837607</v>
+        <v>0.6489583333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05886706706017952</v>
+        <v>0.1020677788841291</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6255369807798379</v>
+        <v>0.508744461420932</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0960485610157089</v>
+        <v>0.1056364356425086</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6171345755693581</v>
+        <v>0.5687121212121211</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1750528142993121</v>
+        <v>0.09989736714752141</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7142472649437134</v>
+        <v>0.5760799632352941</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05736840666982811</v>
+        <v>0.1654468888674703</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.6631578947368422</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1441289481915631</v>
+        <v>0.2749966877282246</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5399799263967882</v>
+        <v>0.6210526315789473</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.45</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5690104166666666</v>
+        <v>0.6992337164750958</v>
       </c>
       <c r="P5" t="n">
-        <v>0.130494950238636</v>
+        <v>0.1685473408437175</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.6657183499288762</v>
       </c>
       <c r="R5" t="n">
-        <v>0.71875</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="T5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U5" t="n">
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="V5" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="W5" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RWD_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.706965811965812</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.06399120156036964</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.6213889730615411</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.08516989809871013</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.7472836438923394</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.1409010961774972</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6388025210084034</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.1261457377705906</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7616666666666667</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.1255909292602578</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.4148936170212766</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.6744791666666667</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.129885402495044</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.6444444444444444</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.65625</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.6458333333333334</v>
-      </c>
-      <c r="T6" t="n">
-        <v>11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>350</v>
-      </c>
-      <c r="V6" t="n">
-        <v>55</v>
-      </c>
-      <c r="W6" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.7248677248677249</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.06355929123713433</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.6246705824080412</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.06052563242756767</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.636655205560485</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.07100871717106204</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.6870631581716488</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.08988036159095726</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.7983333333333333</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.117757770114887</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5271164021164021</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.6733870967741935</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.128510933705694</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.5543916196615633</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.8064516129032258</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.3958333333333333</v>
-      </c>
-      <c r="T7" t="n">
-        <v>12</v>
-      </c>
-      <c r="U7" t="n">
-        <v>336</v>
-      </c>
-      <c r="V7" t="n">
-        <v>55</v>
-      </c>
-      <c r="W7" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6790910808767952</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.06807962180664195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.5712927105310253</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.1171440369689415</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.6379492014196982</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.179744343624796</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6257659276527201</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.2036901213955048</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.7733333333333332</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.1290586392453859</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.4699235626453971</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.6646505376344087</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.1283862088778558</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.4184215031672659</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.9032258064516129</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>336</v>
-      </c>
-      <c r="V8" t="n">
-        <v>55</v>
-      </c>
-      <c r="W8" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8727441860465117</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.06112076353295148</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.7286645554850565</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.075991042741185</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.7208080808080808</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.107599283378963</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.8203709893048128</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.05304369372869949</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.7684210526315791</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2017337995662595</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.5872235872235873</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.7894736842105263</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.5459770114942528</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.1702638396804593</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.5140977443609023</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.5862068965517241</v>
-      </c>
-      <c r="T9" t="n">
-        <v>12</v>
-      </c>
-      <c r="U9" t="n">
-        <v>168</v>
-      </c>
-      <c r="V9" t="n">
-        <v>24</v>
-      </c>
-      <c r="W9" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.6327441860465115</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.09877189114060714</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.3753086021903226</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.1508130617942004</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.6405328798185941</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.3790300093674511</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.4585795255602241</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.32794653767877</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7052631578947368</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2581878322029749</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.5343915343915344</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.4210526315789473</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.6877394636015325</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.1674592721583602</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.6168478260869565</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.5172413793103449</v>
-      </c>
-      <c r="T10" t="n">
-        <v>11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>168</v>
-      </c>
-      <c r="V10" t="n">
-        <v>24</v>
-      </c>
-      <c r="W10" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.7666666666666666</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.0867227063008339</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.6258500158844986</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.08380633352359991</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.7627871067361512</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.07701412930923678</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.6180451479955039</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.1331068342832014</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.5894736842105264</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.2591933471267733</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.4337568058076225</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.4210526315789473</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.6130268199233717</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.1674615713723586</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.5320056899004267</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.2758620689655172</v>
-      </c>
-      <c r="T11" t="n">
-        <v>11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>160</v>
-      </c>
-      <c r="V11" t="n">
-        <v>24</v>
-      </c>
-      <c r="W11" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.6489583333333333</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.1020677788841291</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.508744461420932</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1056364356425086</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.5687121212121211</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.09989736714752141</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.5760799632352941</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.1654468888674703</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.6631578947368422</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.2749966877282246</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.6210526315789473</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.8421052631578947</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.6992337164750958</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.1685473408437175</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.6657183499288762</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.7241379310344828</v>
-      </c>
-      <c r="T12" t="n">
-        <v>11</v>
-      </c>
-      <c r="U12" t="n">
-        <v>160</v>
-      </c>
-      <c r="V12" t="n">
-        <v>24</v>
-      </c>
-      <c r="W12" t="n">
         <v>47</v>
       </c>
     </row>
